--- a/data/trans_dic/P2A_lim_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_lim_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación</t>
+          <t>Hogares con personas con alguna limitación (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 7,49</t>
+          <t>2,27; 7,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,2; 17,68</t>
+          <t>9,28; 17,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,21; 12,06</t>
+          <t>5,28; 12,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,96; 15,53</t>
+          <t>7,87; 15,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,81</t>
+          <t>1,4; 6,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,93; 23,18</t>
+          <t>12,81; 22,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,99; 16,82</t>
+          <t>8,68; 17,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,06; 17,79</t>
+          <t>10,79; 18,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,6</t>
+          <t>2,38; 6,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,2; 18,65</t>
+          <t>11,94; 18,59</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,77; 13,29</t>
+          <t>7,99; 13,02</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,48; 15,69</t>
+          <t>10,19; 15,53</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,31; 13,18</t>
+          <t>7,33; 13,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,45; 13,54</t>
+          <t>7,41; 13,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,07</t>
+          <t>2,48; 6,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,72; 23,78</t>
+          <t>15,48; 23,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,29; 13,89</t>
+          <t>8,4; 13,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,05; 13,45</t>
+          <t>7,8; 13,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,62; 7,77</t>
+          <t>3,65; 7,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,66; 21,75</t>
+          <t>16,01; 21,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,64; 12,63</t>
+          <t>8,48; 12,55</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,33; 12,22</t>
+          <t>8,43; 12,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,58; 6,31</t>
+          <t>3,46; 6,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,49; 21,77</t>
+          <t>16,27; 21,35</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,01</t>
+          <t>1,32; 5,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,55; 14,22</t>
+          <t>6,56; 13,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,14</t>
+          <t>0,99; 4,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,4; 20,32</t>
+          <t>12,56; 20,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,56</t>
+          <t>1,49; 5,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,62; 13,19</t>
+          <t>6,58; 13,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,23</t>
+          <t>2,76; 7,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,64; 16,58</t>
+          <t>10,4; 16,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,53</t>
+          <t>1,76; 4,5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,33; 12,26</t>
+          <t>7,49; 12,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,03</t>
+          <t>2,08; 5,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,43; 17,28</t>
+          <t>12,35; 17,24</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 8,45</t>
+          <t>3,49; 8,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 10,12</t>
+          <t>4,54; 10,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,87; 14,71</t>
+          <t>7,55; 14,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,99; 12,81</t>
+          <t>5,29; 12,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,79; 8,5</t>
+          <t>3,72; 8,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,19; 17,3</t>
+          <t>9,93; 16,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,85; 17,45</t>
+          <t>9,88; 17,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 8,18</t>
+          <t>3,33; 8,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,19; 7,6</t>
+          <t>4,31; 7,61</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,07; 12,73</t>
+          <t>8,19; 12,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,74; 14,68</t>
+          <t>9,68; 15,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,88</t>
+          <t>4,7; 8,91</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,31; 14,46</t>
+          <t>6,23; 14,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,53; 27,33</t>
+          <t>15,47; 27,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,15; 12,93</t>
+          <t>5,16; 12,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,67; 12,36</t>
+          <t>5,43; 12,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,33; 17,74</t>
+          <t>8,62; 18,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,47; 29,13</t>
+          <t>17,25; 28,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,39; 12,64</t>
+          <t>5,0; 12,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,61; 12,2</t>
+          <t>4,49; 12,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,78; 14,69</t>
+          <t>8,63; 14,88</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,94; 26,03</t>
+          <t>17,94; 26,18</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,07; 11,45</t>
+          <t>6,05; 11,49</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,74; 11,0</t>
+          <t>5,65; 10,9</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,32</t>
+          <t>0,37; 3,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,78; 11,65</t>
+          <t>4,74; 11,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,82; 14,26</t>
+          <t>6,87; 14,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20,4; 29,67</t>
+          <t>20,3; 29,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,57</t>
+          <t>1,39; 5,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,34; 17,43</t>
+          <t>9,22; 17,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,04; 16,09</t>
+          <t>8,4; 16,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,2; 28,25</t>
+          <t>19,97; 28,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,68</t>
+          <t>1,15; 3,81</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,04; 13,52</t>
+          <t>8,11; 13,49</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,58; 14,24</t>
+          <t>8,56; 14,39</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21,61; 27,79</t>
+          <t>21,25; 27,32</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,22; 9,09</t>
+          <t>5,05; 9,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,02; 10,4</t>
+          <t>6,0; 10,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,64; 7,48</t>
+          <t>3,7; 7,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,87; 19,06</t>
+          <t>12,76; 19,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,02; 10,28</t>
+          <t>5,81; 10,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,37; 11,67</t>
+          <t>7,08; 11,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,49; 9,86</t>
+          <t>5,35; 9,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,68; 69,37</t>
+          <t>17,58; 69,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,12; 9,12</t>
+          <t>6,02; 8,95</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,23; 10,48</t>
+          <t>7,06; 10,44</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,16; 7,89</t>
+          <t>4,99; 7,98</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,48; 56,27</t>
+          <t>16,54; 58,21</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,41; 10,43</t>
+          <t>6,35; 10,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,18; 10,3</t>
+          <t>6,01; 10,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,62; 11,06</t>
+          <t>6,72; 10,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,5; 8,46</t>
+          <t>2,61; 8,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,42; 14,08</t>
+          <t>9,73; 14,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,84; 10,99</t>
+          <t>6,76; 11,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,14; 11,38</t>
+          <t>6,98; 11,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,04; 11,73</t>
+          <t>7,97; 11,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,59; 11,6</t>
+          <t>8,51; 11,69</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,91; 9,8</t>
+          <t>6,94; 9,84</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,55; 10,65</t>
+          <t>7,48; 10,58</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,3; 9,33</t>
+          <t>4,57; 9,27</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,81; 7,58</t>
+          <t>5,81; 7,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,53; 10,68</t>
+          <t>8,47; 10,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,15; 8,06</t>
+          <t>6,12; 7,97</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,22; 14,51</t>
+          <t>9,85; 14,55</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,16; 9,11</t>
+          <t>7,1; 8,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,46; 12,66</t>
+          <t>10,45; 12,78</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,77; 9,71</t>
+          <t>7,79; 9,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,52; 33,16</t>
+          <t>13,43; 33,32</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,76; 8,02</t>
+          <t>6,77; 8,05</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9,8; 11,25</t>
+          <t>9,81; 11,36</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,25; 8,56</t>
+          <t>7,23; 8,62</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,02; 27,71</t>
+          <t>13,0; 26,03</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación</t>
+          <t>Hogares con personas con alguna limitación (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6029; 20321</t>
+          <t>6149; 20842</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27126; 52110</t>
+          <t>27352; 52041</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15297; 35416</t>
+          <t>15507; 35403</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24778; 48371</t>
+          <t>24511; 48473</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3241; 15085</t>
+          <t>3635; 15961</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37140; 66578</t>
+          <t>36790; 65344</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25955; 48570</t>
+          <t>25048; 49331</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32041; 51513</t>
+          <t>31254; 52249</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12105; 29756</t>
+          <t>12612; 33189</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>71012; 108557</t>
+          <t>69488; 108196</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45233; 77385</t>
+          <t>46529; 75862</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>63018; 94321</t>
+          <t>61276; 93334</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36037; 64986</t>
+          <t>36153; 65425</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37661; 68467</t>
+          <t>37483; 67061</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12437; 29810</t>
+          <t>12173; 29981</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80874; 122346</t>
+          <t>79652; 122013</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41779; 70022</t>
+          <t>42346; 70022</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42170; 70448</t>
+          <t>40854; 69254</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18758; 40247</t>
+          <t>18900; 39980</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>80312; 111581</t>
+          <t>82107; 111969</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>86139; 125922</t>
+          <t>84501; 125123</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85791; 125782</t>
+          <t>86725; 126137</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36097; 63649</t>
+          <t>34970; 63342</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>169458; 223668</t>
+          <t>167103; 219314</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3932; 15984</t>
+          <t>4201; 16763</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21217; 46093</t>
+          <t>21267; 44476</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2492; 13190</t>
+          <t>3138; 13540</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39083; 64043</t>
+          <t>39577; 64716</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5254; 18664</t>
+          <t>5014; 17306</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22585; 44997</t>
+          <t>22424; 45079</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9024; 24305</t>
+          <t>9287; 23922</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37148; 57887</t>
+          <t>36322; 56167</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12187; 29622</t>
+          <t>11537; 29438</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48735; 81541</t>
+          <t>49790; 82409</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13710; 32911</t>
+          <t>13621; 32719</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>82597; 114787</t>
+          <t>82063; 114527</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12227; 30058</t>
+          <t>12396; 30385</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17216; 37854</t>
+          <t>16988; 37727</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29120; 54431</t>
+          <t>27940; 52651</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15491; 39739</t>
+          <t>16410; 38734</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14087; 31587</t>
+          <t>13803; 32153</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39634; 67294</t>
+          <t>38641; 65913</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38157; 67571</t>
+          <t>38256; 66369</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15834; 38890</t>
+          <t>15846; 38446</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30431; 55276</t>
+          <t>31303; 55303</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>61558; 97157</t>
+          <t>62516; 95703</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73776; 111153</t>
+          <t>73304; 114124</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>35803; 69825</t>
+          <t>36908; 70054</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12825; 29399</t>
+          <t>12662; 30024</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>33026; 58100</t>
+          <t>32900; 58849</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10873; 27309</t>
+          <t>10907; 26610</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9793; 21334</t>
+          <t>9371; 21233</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17290; 36837</t>
+          <t>17905; 37460</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38354; 63958</t>
+          <t>37873; 61872</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11780; 27619</t>
+          <t>10925; 27979</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11512; 30472</t>
+          <t>11218; 30136</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>36069; 60352</t>
+          <t>35459; 61154</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>77548; 112497</t>
+          <t>77533; 113141</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26080; 49211</t>
+          <t>26023; 49368</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>24257; 46450</t>
+          <t>23871; 46054</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>987; 8917</t>
+          <t>983; 8782</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13099; 31930</t>
+          <t>12992; 30690</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17951; 37515</t>
+          <t>18079; 38224</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>54994; 80003</t>
+          <t>54740; 78630</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3918; 15488</t>
+          <t>3855; 16164</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26142; 48805</t>
+          <t>25808; 49423</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21970; 43935</t>
+          <t>22942; 44706</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>51913; 72629</t>
+          <t>51331; 72984</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6789; 20138</t>
+          <t>6317; 20821</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>44563; 74907</t>
+          <t>44945; 74760</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>45995; 76374</t>
+          <t>45882; 77174</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>113831; 146380</t>
+          <t>111934; 143888</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>32098; 55913</t>
+          <t>31029; 57305</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>39854; 68852</t>
+          <t>39685; 68713</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23666; 48699</t>
+          <t>24063; 48165</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>79375; 117509</t>
+          <t>78696; 118211</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>38423; 65636</t>
+          <t>37050; 64574</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>50999; 80766</t>
+          <t>48965; 82902</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37847; 67969</t>
+          <t>36884; 66647</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>149724; 587633</t>
+          <t>148875; 585391</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>76644; 114253</t>
+          <t>75439; 112189</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>97837; 141932</t>
+          <t>95616; 141267</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>69220; 105772</t>
+          <t>66826; 106951</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>241247; 823551</t>
+          <t>242152; 851987</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>47536; 77324</t>
+          <t>47058; 77945</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>47991; 80000</t>
+          <t>46695; 79396</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>51548; 86075</t>
+          <t>52301; 84984</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>23144; 78394</t>
+          <t>24161; 78635</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>73540; 109870</t>
+          <t>75914; 111797</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>56313; 90560</t>
+          <t>55720; 90626</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>59003; 94039</t>
+          <t>57638; 94220</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>57466; 83798</t>
+          <t>56939; 81854</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>130645; 176551</t>
+          <t>129478; 177924</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>110667; 156839</t>
+          <t>111082; 157446</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>121128; 170853</t>
+          <t>119983; 169820</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>70555; 153090</t>
+          <t>74976; 152085</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>189845; 247810</t>
+          <t>189776; 248188</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>291937; 365686</t>
+          <t>290109; 363057</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>207562; 272160</t>
+          <t>206871; 269362</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>351263; 498687</t>
+          <t>338505; 500210</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>241531; 307359</t>
+          <t>239778; 302984</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>372104; 450408</t>
+          <t>371795; 454340</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>274838; 343545</t>
+          <t>275698; 343640</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>499800; 1225374</t>
+          <t>496321; 1231422</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>448730; 532442</t>
+          <t>449897; 534914</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>683949; 785386</t>
+          <t>684420; 792609</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>501359; 591663</t>
+          <t>500086; 596343</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>928987; 1976213</t>
+          <t>927262; 1857005</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_lim_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_lim_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 7,68</t>
+          <t>2,06; 7,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,28; 17,66</t>
+          <t>9,18; 17,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,28; 12,05</t>
+          <t>5,25; 11,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,87; 15,56</t>
+          <t>7,3; 14,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 6,15</t>
+          <t>1,55; 6,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,81; 22,75</t>
+          <t>12,8; 22,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,68; 17,09</t>
+          <t>8,65; 16,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,79; 18,04</t>
+          <t>10,31; 16,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,25</t>
+          <t>2,34; 5,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,94; 18,59</t>
+          <t>11,72; 18,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,99; 13,02</t>
+          <t>7,86; 13,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,19; 15,53</t>
+          <t>9,93; 14,47</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,33; 13,27</t>
+          <t>7,47; 13,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,41; 13,27</t>
+          <t>7,33; 13,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 6,1</t>
+          <t>2,54; 6,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,48; 23,72</t>
+          <t>15,32; 23,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,4; 13,89</t>
+          <t>8,23; 13,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,8; 13,22</t>
+          <t>7,78; 13,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,72</t>
+          <t>3,81; 7,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,01; 21,83</t>
+          <t>15,86; 21,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,48; 12,55</t>
+          <t>8,45; 12,35</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,43; 12,25</t>
+          <t>8,36; 12,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 6,28</t>
+          <t>3,54; 6,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,27; 21,35</t>
+          <t>16,6; 21,56</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,26</t>
+          <t>1,26; 4,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 13,73</t>
+          <t>6,49; 14,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,25</t>
+          <t>0,83; 4,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,56; 20,54</t>
+          <t>12,8; 20,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,16</t>
+          <t>1,55; 5,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,58; 13,22</t>
+          <t>6,65; 13,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 7,11</t>
+          <t>2,77; 7,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,4; 16,09</t>
+          <t>10,42; 15,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,5</t>
+          <t>1,88; 4,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 12,39</t>
+          <t>7,27; 11,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,0</t>
+          <t>2,1; 4,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,35; 17,24</t>
+          <t>12,26; 16,94</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,49; 8,54</t>
+          <t>3,54; 8,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 10,09</t>
+          <t>4,81; 10,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,55; 14,23</t>
+          <t>7,86; 14,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,29; 12,48</t>
+          <t>5,17; 12,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,72; 8,66</t>
+          <t>3,59; 8,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,93; 16,95</t>
+          <t>9,88; 16,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,88; 17,14</t>
+          <t>10,18; 17,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 8,08</t>
+          <t>5,13; 9,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 7,61</t>
+          <t>4,16; 7,53</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,19; 12,54</t>
+          <t>8,15; 12,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,68; 15,07</t>
+          <t>9,69; 14,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,7; 8,91</t>
+          <t>5,84; 10,03</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,23; 14,77</t>
+          <t>6,33; 14,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,47; 27,68</t>
+          <t>15,25; 27,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,16; 12,6</t>
+          <t>5,31; 12,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,43; 12,3</t>
+          <t>5,18; 10,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,62; 18,04</t>
+          <t>8,7; 18,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,25; 28,18</t>
+          <t>17,43; 29,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,0; 12,8</t>
+          <t>5,27; 12,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,49; 12,07</t>
+          <t>8,43; 14,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,63; 14,88</t>
+          <t>8,6; 14,87</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,94; 26,18</t>
+          <t>17,61; 26,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,05; 11,49</t>
+          <t>6,0; 11,21</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,65; 10,9</t>
+          <t>7,53; 11,7</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,27</t>
+          <t>0,38; 3,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,74; 11,2</t>
+          <t>5,16; 11,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,87; 14,53</t>
+          <t>6,64; 14,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20,3; 29,16</t>
+          <t>20,28; 28,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,39; 5,81</t>
+          <t>1,39; 5,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,22; 17,65</t>
+          <t>9,4; 17,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,4; 16,37</t>
+          <t>8,15; 16,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,97; 28,39</t>
+          <t>19,93; 27,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,81</t>
+          <t>1,25; 3,76</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,11; 13,49</t>
+          <t>7,98; 13,23</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,56; 14,39</t>
+          <t>8,5; 14,05</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21,25; 27,32</t>
+          <t>21,45; 27,64</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,05; 9,32</t>
+          <t>5,22; 9,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,0; 10,38</t>
+          <t>6,24; 10,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,4</t>
+          <t>3,83; 7,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,76; 19,17</t>
+          <t>13,6; 19,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,81; 10,12</t>
+          <t>5,88; 10,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,08; 11,98</t>
+          <t>6,96; 11,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,35; 9,67</t>
+          <t>5,45; 10,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,58; 69,11</t>
+          <t>17,27; 22,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,02; 8,95</t>
+          <t>6,08; 8,99</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,06; 10,44</t>
+          <t>7,27; 10,58</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,99; 7,98</t>
+          <t>5,16; 7,97</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,54; 58,21</t>
+          <t>16,0; 20,24</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,35; 10,52</t>
+          <t>6,39; 10,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,01; 10,22</t>
+          <t>6,0; 10,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,72; 10,92</t>
+          <t>6,63; 10,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,61; 8,48</t>
+          <t>5,98; 9,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,73; 14,32</t>
+          <t>9,51; 14,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,76; 11,0</t>
+          <t>6,76; 10,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,98; 11,4</t>
+          <t>7,1; 11,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,97; 11,46</t>
+          <t>8,27; 12,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,51; 11,69</t>
+          <t>8,44; 11,64</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,94; 9,84</t>
+          <t>6,99; 9,86</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,48; 10,58</t>
+          <t>7,43; 10,42</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,57; 9,27</t>
+          <t>7,71; 10,47</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,81; 7,6</t>
+          <t>5,79; 7,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,47; 10,6</t>
+          <t>8,52; 10,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,12; 7,97</t>
+          <t>6,06; 7,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,85; 14,55</t>
+          <t>12,22; 14,7</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,1; 8,98</t>
+          <t>7,24; 9,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,45; 12,78</t>
+          <t>10,45; 12,76</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,79; 9,71</t>
+          <t>7,8; 9,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,43; 33,32</t>
+          <t>13,53; 15,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,77; 8,05</t>
+          <t>6,75; 8,01</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9,81; 11,36</t>
+          <t>9,8; 11,37</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,23; 8,62</t>
+          <t>7,26; 8,58</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,0; 26,03</t>
+          <t>13,26; 14,85</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34985</t>
+          <t>34128</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40947</t>
+          <t>41656</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75932</t>
+          <t>75785</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6149; 20842</t>
+          <t>5601; 20308</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27352; 52041</t>
+          <t>27063; 51076</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15507; 35403</t>
+          <t>15418; 34962</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24511; 48473</t>
+          <t>23276; 45970</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3635; 15961</t>
+          <t>4029; 16332</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36790; 65344</t>
+          <t>36761; 64611</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25048; 49331</t>
+          <t>24962; 48420</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31254; 52249</t>
+          <t>32601; 52360</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12612; 33189</t>
+          <t>12425; 30331</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>69488; 108196</t>
+          <t>68188; 106464</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46529; 75862</t>
+          <t>45790; 77336</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>61276; 93334</t>
+          <t>63022; 91842</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>98843</t>
+          <t>100833</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>95835</t>
+          <t>101575</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>194678</t>
+          <t>202408</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36153; 65425</t>
+          <t>36820; 65402</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37483; 67061</t>
+          <t>37038; 66621</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12173; 29981</t>
+          <t>12476; 29992</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79652; 122013</t>
+          <t>80786; 124040</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42346; 70022</t>
+          <t>41474; 68713</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40854; 69254</t>
+          <t>40775; 69184</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18900; 39980</t>
+          <t>19754; 41375</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>82107; 111969</t>
+          <t>86372; 118292</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>84501; 125123</t>
+          <t>84294; 123159</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>86725; 126137</t>
+          <t>86050; 125860</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34970; 63342</t>
+          <t>35780; 64314</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>167103; 219314</t>
+          <t>177919; 231090</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51309</t>
+          <t>50796</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>45768</t>
+          <t>46324</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97077</t>
+          <t>97120</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4201; 16763</t>
+          <t>4009; 15560</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21267; 44476</t>
+          <t>21047; 46665</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3138; 13540</t>
+          <t>2638; 13740</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39577; 64716</t>
+          <t>40334; 64344</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5014; 17306</t>
+          <t>5213; 17998</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22424; 45079</t>
+          <t>22666; 45061</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9287; 23922</t>
+          <t>9299; 24733</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36322; 56167</t>
+          <t>37136; 56939</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11537; 29438</t>
+          <t>12325; 29877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49790; 82409</t>
+          <t>48374; 79468</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13621; 32719</t>
+          <t>13740; 32433</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>82063; 114527</t>
+          <t>82337; 113769</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25220</t>
+          <t>30607</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>26994</t>
+          <t>29140</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>52214</t>
+          <t>59747</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12396; 30385</t>
+          <t>12607; 30406</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16988; 37727</t>
+          <t>17981; 37888</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27940; 52651</t>
+          <t>29076; 53026</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16410; 38734</t>
+          <t>19171; 47669</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13803; 32153</t>
+          <t>13347; 31893</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38641; 65913</t>
+          <t>38411; 65993</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38256; 66369</t>
+          <t>39414; 67077</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15846; 38446</t>
+          <t>21666; 42160</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>31303; 55303</t>
+          <t>30270; 54736</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62516; 95703</t>
+          <t>62165; 96486</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73304; 114124</t>
+          <t>73390; 112113</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>36908; 70054</t>
+          <t>46296; 79485</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14303</t>
+          <t>15657</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>22040</t>
+          <t>23815</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36343</t>
+          <t>39472</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12662; 30024</t>
+          <t>12869; 29326</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>32900; 58849</t>
+          <t>32422; 57931</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10907; 26610</t>
+          <t>11225; 27174</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9371; 21233</t>
+          <t>10320; 21827</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17905; 37460</t>
+          <t>18059; 37593</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37873; 61872</t>
+          <t>38273; 63671</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10925; 27979</t>
+          <t>11509; 28143</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11218; 30136</t>
+          <t>18458; 30801</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35459; 61154</t>
+          <t>35338; 61121</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>77533; 113141</t>
+          <t>76119; 112652</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26023; 49368</t>
+          <t>25776; 48166</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>23871; 46054</t>
+          <t>31496; 48902</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66533</t>
+          <t>66441</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>61876</t>
+          <t>62441</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>128409</t>
+          <t>128882</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>983; 8782</t>
+          <t>1017; 9750</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12992; 30690</t>
+          <t>14148; 31112</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18079; 38224</t>
+          <t>17479; 38123</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>54740; 78630</t>
+          <t>54910; 78164</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3855; 16164</t>
+          <t>3876; 15770</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25808; 49423</t>
+          <t>26315; 50030</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22942; 44706</t>
+          <t>22246; 45879</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>51331; 72984</t>
+          <t>52569; 73379</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6317; 20821</t>
+          <t>6839; 20577</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>44945; 74760</t>
+          <t>44200; 73287</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>45882; 77174</t>
+          <t>45594; 75338</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>111934; 143888</t>
+          <t>114622; 147733</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>97267</t>
+          <t>114028</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>323676</t>
+          <t>151370</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>420943</t>
+          <t>265398</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>31029; 57305</t>
+          <t>32121; 57662</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>39685; 68713</t>
+          <t>41272; 70920</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24063; 48165</t>
+          <t>24958; 48348</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>78696; 118211</t>
+          <t>96221; 137265</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>37050; 64574</t>
+          <t>37529; 64267</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>48965; 82902</t>
+          <t>48182; 80321</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36884; 66647</t>
+          <t>37580; 70053</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>148875; 585391</t>
+          <t>132956; 174812</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>75439; 112189</t>
+          <t>76212; 112692</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>95616; 141267</t>
+          <t>98438; 143224</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>66826; 106951</t>
+          <t>69167; 106803</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>242152; 851987</t>
+          <t>236356; 299104</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>53746</t>
+          <t>62220</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>69491</t>
+          <t>82936</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>123237</t>
+          <t>145156</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>47058; 77945</t>
+          <t>47394; 77833</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>46695; 79396</t>
+          <t>46627; 79942</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>52301; 84984</t>
+          <t>51631; 85066</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>24161; 78635</t>
+          <t>47593; 78460</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>75914; 111797</t>
+          <t>74227; 110673</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>55720; 90626</t>
+          <t>55726; 90084</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>57638; 94220</t>
+          <t>58627; 93891</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>56939; 81854</t>
+          <t>68455; 99509</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>129478; 177924</t>
+          <t>128436; 177180</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>111082; 157446</t>
+          <t>111912; 157862</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>119983; 169820</t>
+          <t>119210; 167231</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>74976; 152085</t>
+          <t>125232; 170038</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>442206</t>
+          <t>474711</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>686628</t>
+          <t>539257</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1128833</t>
+          <t>1013967</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>189776; 248188</t>
+          <t>189238; 250372</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>290109; 363057</t>
+          <t>291578; 364317</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>206871; 269362</t>
+          <t>204528; 268352</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>338505; 500210</t>
+          <t>428364; 515490</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>239778; 302984</t>
+          <t>244338; 305926</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>371795; 454340</t>
+          <t>371725; 453782</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>275698; 343640</t>
+          <t>275777; 345368</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>496321; 1231422</t>
+          <t>503319; 576475</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>449897; 534914</t>
+          <t>448197; 532244</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>684420; 792609</t>
+          <t>683989; 793306</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>500086; 596343</t>
+          <t>501779; 593632</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>927262; 1857005</t>
+          <t>957866; 1073169</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_lim_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_lim_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación (tasa de respuesta: 99,66%)</t>
+          <t>Población que convive con personas con alguna limitación (física, sensorial o psíquica) (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación (tasa de respuesta: 99,66%)</t>
+          <t>Población que convive con personas con alguna limitación (física, sensorial o psíquica) (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
